--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_menu_layer.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_menu_layer.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_menu_layer" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="48">
   <si>
     <t>唯一id</t>
   </si>
@@ -122,40 +122,52 @@
     <t>商城</t>
   </si>
   <si>
+    <t>积分商城</t>
+  </si>
+  <si>
+    <t>10010001#10240001#10040001</t>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
     <t>积分商店</t>
   </si>
   <si>
+    <t>药水类</t>
+  </si>
+  <si>
+    <t>道具类</t>
+  </si>
+  <si>
+    <t>1032</t>
+  </si>
+  <si>
+    <t>职业卡</t>
+  </si>
+  <si>
+    <t>消耗类</t>
+  </si>
+  <si>
+    <t>转职物品</t>
+  </si>
+  <si>
+    <t>瑞币</t>
+  </si>
+  <si>
+    <t>瑞币商店</t>
+  </si>
+  <si>
+    <t>称号</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>强力技能</t>
+  </si>
+  <si>
     <t>10010001#10240001#10250001</t>
-  </si>
-  <si>
-    <t>1030</t>
-  </si>
-  <si>
-    <t>增益buff</t>
-  </si>
-  <si>
-    <t>道具商店</t>
-  </si>
-  <si>
-    <t>1032</t>
-  </si>
-  <si>
-    <t>职业卡</t>
-  </si>
-  <si>
-    <t>金币兑换</t>
-  </si>
-  <si>
-    <t>转职物品</t>
-  </si>
-  <si>
-    <t>1033</t>
-  </si>
-  <si>
-    <t>积分商城</t>
-  </si>
-  <si>
-    <t>强力技能</t>
   </si>
   <si>
     <t>活动商城</t>
@@ -1330,7 +1342,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="26.7142857142857" customWidth="1"/>
@@ -1480,10 +1492,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
         <v>31</v>
@@ -1503,10 +1515,10 @@
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -1517,7 +1529,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1526,10 +1538,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
         <v>31</v>
@@ -1549,10 +1561,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
         <v>31</v>
@@ -1572,15 +1584,130 @@
         <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
         <v>31</v>
       </c>
       <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:8">
+      <c r="A11">
+        <v>1004</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:8">
+      <c r="A12">
+        <v>5001</v>
+      </c>
+      <c r="B12">
+        <v>1004</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:8">
+      <c r="A13">
+        <v>5002</v>
+      </c>
+      <c r="B13">
+        <v>1004</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:8">
+      <c r="A14">
+        <v>5003</v>
+      </c>
+      <c r="B14">
+        <v>1004</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:8">
+      <c r="A15">
+        <v>5004</v>
+      </c>
+      <c r="B15">
+        <v>1004</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15">
         <v>0</v>
       </c>
     </row>
@@ -1599,7 +1726,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
         <v>27</v>
@@ -1608,13 +1735,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G1">
         <v>9999</v>
@@ -1634,7 +1761,7 @@
         <v>29</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G2" s="1">
         <v>9999</v>
@@ -1651,10 +1778,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F3" s="1">
         <v>10230001</v>
@@ -1677,10 +1804,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F4" s="1">
         <v>10230001</v>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_menu_layer.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_menu_layer.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_menu_layer" sheetId="1" r:id="rId1"/>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
   <si>
     <t>唯一id</t>
   </si>
@@ -125,9 +130,6 @@
     <t>积分商城</t>
   </si>
   <si>
-    <t>10010001#10240001#10040001</t>
-  </si>
-  <si>
     <t>1030</t>
   </si>
   <si>
@@ -158,7 +160,22 @@
     <t>瑞币商店</t>
   </si>
   <si>
-    <t>称号</t>
+    <t>增益类</t>
+  </si>
+  <si>
+    <t>大天使积分</t>
+  </si>
+  <si>
+    <t>大天使商城</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>防具</t>
+  </si>
+  <si>
+    <t>材料</t>
   </si>
   <si>
     <t>1033</t>
@@ -186,7 +203,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -195,6 +212,12 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -652,152 +675,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -808,6 +831,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -861,7 +887,24 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="19">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1055,25 +1098,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="totalRow" dxfId="6"/>
+      <tableStyleElement type="firstColumn" dxfId="5"/>
+      <tableStyleElement type="lastColumn" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1342,7 +1385,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="26.7142857142857" customWidth="1"/>
@@ -1474,8 +1517,8 @@
       <c r="E5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
-        <v>31</v>
+      <c r="F5">
+        <v>10240001</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1483,7 +1526,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -1492,16 +1535,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
+      <c r="F6">
+        <v>10240001</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1515,13 +1558,13 @@
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <v>10240001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1529,7 +1572,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1538,16 +1581,16 @@
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>10240001</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1561,13 +1604,13 @@
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
+        <v>37</v>
+      </c>
+      <c r="F9">
+        <v>10240001</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1584,13 +1627,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="F10">
+        <v>10240001</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1607,13 +1650,13 @@
         <v>3</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
+      <c r="F11">
+        <v>10040001</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1630,13 +1673,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
+      <c r="F12">
+        <v>10040001</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1653,65 +1696,119 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F13">
+        <v>10040001</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:8">
+    <row r="14" customFormat="1" ht="16.5" spans="1:8">
       <c r="A14">
-        <v>5003</v>
-      </c>
-      <c r="B14">
-        <v>1004</v>
+        <v>1005</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" t="s">
-        <v>31</v>
+        <v>43</v>
+      </c>
+      <c r="F14" s="5">
+        <v>10210001</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="1:8">
+    <row r="15" customFormat="1" ht="16.5" spans="1:8">
       <c r="A15">
-        <v>5004</v>
+        <v>6001</v>
       </c>
       <c r="B15">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" t="s">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10210001</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
     </row>
+    <row r="16" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A16">
+        <v>6002</v>
+      </c>
+      <c r="B16">
+        <v>1005</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="5">
+        <v>10210001</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="16.5" spans="1:7">
+      <c r="A17">
+        <v>6003</v>
+      </c>
+      <c r="B17">
+        <v>1005</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="5">
+        <v>10210001</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F16">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1726,7 +1823,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
         <v>27</v>
@@ -1738,10 +1835,10 @@
         <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G1">
         <v>9999</v>
@@ -1761,7 +1858,7 @@
         <v>29</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G2" s="1">
         <v>9999</v>
@@ -1778,10 +1875,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F3" s="1">
         <v>10230001</v>
@@ -1804,10 +1901,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F4" s="1">
         <v>10230001</v>
